--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90207</v>
+        <v>90217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90217</v>
+        <v>90229</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90229</v>
+        <v>90230</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90230</v>
+        <v>90233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90233</v>
+        <v>90239</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90239</v>
+        <v>90240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,6 +2220,210 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122185443</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90754</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571227</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6715301</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122185453</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91194</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571161</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6715374</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>90754</v>
+        <v>91194</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R15" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>91194</v>
+        <v>90754</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R16" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>91194</v>
+        <v>91201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>90754</v>
+        <v>90761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>90779</v>
+        <v>91219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R15" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>91219</v>
+        <v>90779</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R16" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B15" t="n">
-        <v>91219</v>
+        <v>90789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R15" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B16" t="n">
-        <v>90779</v>
+        <v>91229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R16" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>90789</v>
+        <v>91229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R15" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>91229</v>
+        <v>90789</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R16" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B15" t="n">
-        <v>91229</v>
+        <v>90801</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R15" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B16" t="n">
-        <v>90789</v>
+        <v>91241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R16" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>90801</v>
+        <v>91246</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R15" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>91241</v>
+        <v>90808</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R16" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B15" t="n">
-        <v>91246</v>
+        <v>90813</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R15" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B16" t="n">
-        <v>90808</v>
+        <v>91251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2331,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R16" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122185443</v>
       </c>
       <c r="B15" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2239,6 +2239,11 @@
       </c>
       <c r="E15" t="n">
         <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2322,7 +2327,7 @@
         <v>122185453</v>
       </c>
       <c r="B16" t="n">
-        <v>91251</v>
+        <v>91264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,6 +2341,11 @@
       </c>
       <c r="E16" t="n">
         <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B15" t="n">
-        <v>90826</v>
+        <v>91277</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R15" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B16" t="n">
-        <v>91264</v>
+        <v>90839</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R16" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122185453</v>
+        <v>122185443</v>
       </c>
       <c r="B15" t="n">
-        <v>91277</v>
+        <v>90839</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571161</v>
+        <v>571227</v>
       </c>
       <c r="R15" t="n">
-        <v>6715374</v>
+        <v>6715301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122185443</v>
+        <v>122185453</v>
       </c>
       <c r="B16" t="n">
-        <v>90839</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571227</v>
+        <v>571161</v>
       </c>
       <c r="R16" t="n">
-        <v>6715301</v>
+        <v>6715374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,6 +2424,588 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128358044</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92664</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brödtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum versipelle</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571470</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6715422</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128357425</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74965</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571634</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6715465</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128358467</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571523</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6715484</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128358219</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lissjö fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571538</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6715392</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128357954</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91567</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571470</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6715422</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128358024</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92647</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>788</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>571470</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6715422</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92664</v>
+        <v>92669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>74965</v>
+        <v>74966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>91373</v>
+        <v>91378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91567</v>
+        <v>91572</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92647</v>
+        <v>92652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92669</v>
+        <v>92761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>74966</v>
+        <v>74981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91572</v>
+        <v>91664</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
+        <v>92734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R19" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B20" t="n">
-        <v>92734</v>
+        <v>91470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R20" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92761</v>
+        <v>92773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>74981</v>
+        <v>74985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>92734</v>
+        <v>91482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R19" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>91470</v>
+        <v>92746</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R20" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91664</v>
+        <v>91676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92773</v>
+        <v>92775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>74985</v>
+        <v>74987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B19" t="n">
-        <v>91482</v>
+        <v>92748</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R19" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B20" t="n">
-        <v>92746</v>
+        <v>91484</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R20" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91676</v>
+        <v>91678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>92748</v>
+        <v>91485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R19" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>91484</v>
+        <v>92749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R20" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92776</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>74987</v>
+        <v>75014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91679</v>
+        <v>91706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92803</v>
+        <v>92813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>75014</v>
+        <v>75015</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91706</v>
+        <v>91716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92786</v>
+        <v>92796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>92786</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R19" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B20" t="n">
-        <v>92786</v>
+        <v>91522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R20" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>92786</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R19" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>91522</v>
+        <v>92786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R20" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2429,7 +2429,7 @@
         <v>128358044</v>
       </c>
       <c r="B17" t="n">
-        <v>92813</v>
+        <v>92817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128357425</v>
       </c>
       <c r="B18" t="n">
-        <v>75015</v>
+        <v>75019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128358467</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>128358219</v>
       </c>
       <c r="B20" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>128357954</v>
       </c>
       <c r="B21" t="n">
-        <v>91716</v>
+        <v>91720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>128358024</v>
       </c>
       <c r="B22" t="n">
-        <v>92796</v>
+        <v>92800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128358467</v>
+        <v>128358219</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>92790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,34 +2631,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lissjön, Gstr</t>
+          <t>Lissjö fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571523</v>
+        <v>571538</v>
       </c>
       <c r="R19" t="n">
-        <v>6715484</v>
+        <v>6715392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128358219</v>
+        <v>128358467</v>
       </c>
       <c r="B20" t="n">
-        <v>92790</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lissjö fäbodar, Gstr</t>
+          <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571538</v>
+        <v>571523</v>
       </c>
       <c r="R20" t="n">
-        <v>6715392</v>
+        <v>6715484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,12 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>90240</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dialog hos validator</t>
-        </is>
+        <v>91057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91057</v>
+        <v>91059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91059</v>
+        <v>91060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91060</v>
+        <v>91063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91063</v>
+        <v>91065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91065</v>
+        <v>91069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91069</v>
+        <v>91070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91070</v>
+        <v>91073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91073</v>
+        <v>91101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91101</v>
+        <v>91107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91107</v>
+        <v>91108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>95874692</v>
       </c>
       <c r="B10" t="n">
-        <v>91108</v>
+        <v>91113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,1798 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131521262</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57888</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>571541</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6715550</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131521271</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>571531</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6715557</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131521265</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>571411</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6715454</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131521261</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57888</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>571641</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6715511</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Dagsfärska spår efter födosök</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131521216</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>571514</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6715445</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131521234</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>571695</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6715472</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I intakt boträd</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131521225</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57888</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571575</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6715423</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131521256</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92464</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>571363</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6715404</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131521231</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>571602</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6715612</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131521236</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>571703</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6715471</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131521223</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92540</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571223</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6715293</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131521228</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571409</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6715460</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131521237</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>571464</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6715535</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>I högstubbe</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131521257</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91191</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>571370</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6715387</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131521239</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57888</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>571698</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6715463</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131521270</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lissjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>571209</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6715425</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -4016,38 +4016,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131521236</v>
+        <v>131521228</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>4773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571703</v>
+        <v>571409</v>
       </c>
       <c r="R32" t="n">
-        <v>6715471</v>
+        <v>6715460</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,45 +4128,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131521223</v>
+        <v>131521236</v>
       </c>
       <c r="B33" t="n">
-        <v>92540</v>
+        <v>57885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571223</v>
+        <v>571703</v>
       </c>
       <c r="R33" t="n">
-        <v>6715293</v>
+        <v>6715471</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,7 +4203,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4208,7 +4213,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4235,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131521228</v>
+        <v>131521223</v>
       </c>
       <c r="B34" t="n">
-        <v>4773</v>
+        <v>92540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4246,39 +4251,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100299</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571409</v>
+        <v>571223</v>
       </c>
       <c r="R34" t="n">
-        <v>6715460</v>
+        <v>6715293</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -3006,7 +3006,7 @@
         <v>131521262</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,50 +3227,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131521265</v>
+        <v>131521216</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>91821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571411</v>
+        <v>571514</v>
       </c>
       <c r="R25" t="n">
-        <v>6715454</v>
+        <v>6715445</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3302,7 +3297,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,7 +3307,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,38 +3334,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131521261</v>
+        <v>131521265</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>5177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3379,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571641</v>
+        <v>571411</v>
       </c>
       <c r="R26" t="n">
-        <v>6715511</v>
+        <v>6715454</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,12 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Dagsfärska spår efter födosök</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3456,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131521216</v>
+        <v>131521261</v>
       </c>
       <c r="B27" t="n">
-        <v>91818</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,34 +3457,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571514</v>
+        <v>571641</v>
       </c>
       <c r="R27" t="n">
-        <v>6715445</v>
+        <v>6715511</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3521,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3536,7 +3531,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Dagsfärska spår efter födosök</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131521234</v>
+        <v>131521225</v>
       </c>
       <c r="B28" t="n">
-        <v>57885</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3592,9 +3592,14 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3603,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571695</v>
+        <v>571575</v>
       </c>
       <c r="R28" t="n">
-        <v>6715472</v>
+        <v>6715423</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,7 +3643,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3648,12 +3653,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>I intakt boträd</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131521225</v>
+        <v>131521234</v>
       </c>
       <c r="B29" t="n">
         <v>57888</v>
@@ -3691,16 +3691,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3709,14 +3709,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3725,10 +3720,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571575</v>
+        <v>571695</v>
       </c>
       <c r="R29" t="n">
-        <v>6715423</v>
+        <v>6715472</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,7 +3755,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,7 +3765,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I intakt boträd</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,7 +3800,7 @@
         <v>131521256</v>
       </c>
       <c r="B30" t="n">
-        <v>92464</v>
+        <v>92467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131521228</v>
+        <v>131521223</v>
       </c>
       <c r="B32" t="n">
-        <v>4773</v>
+        <v>92543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,39 +4027,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100299</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571409</v>
+        <v>571223</v>
       </c>
       <c r="R32" t="n">
-        <v>6715460</v>
+        <v>6715293</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4091,7 +4086,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4101,7 +4096,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,7 +4126,7 @@
         <v>131521236</v>
       </c>
       <c r="B33" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4240,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131521223</v>
+        <v>131521228</v>
       </c>
       <c r="B34" t="n">
-        <v>92540</v>
+        <v>4773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,34 +4246,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lissjön, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571223</v>
+        <v>571409</v>
       </c>
       <c r="R34" t="n">
-        <v>6715293</v>
+        <v>6715460</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4350,7 +4350,7 @@
         <v>131521237</v>
       </c>
       <c r="B35" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>131521257</v>
       </c>
       <c r="B36" t="n">
-        <v>91191</v>
+        <v>91194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>131521239</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 65026-2021 artfynd.xlsx
+++ b/artfynd/A 65026-2021 artfynd.xlsx
@@ -3006,7 +3006,7 @@
         <v>131521262</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>131521216</v>
       </c>
       <c r="B25" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>131521261</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131521225</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>131521234</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>131521256</v>
       </c>
       <c r="B30" t="n">
-        <v>92467</v>
+        <v>92468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>131521223</v>
       </c>
       <c r="B32" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>131521236</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>131521237</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>131521257</v>
       </c>
       <c r="B36" t="n">
-        <v>91194</v>
+        <v>91195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>131521239</v>
       </c>
       <c r="B37" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
